--- a/data/trans_camb/P43E-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P43E-Estudios-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>-6,44</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -4,01</t>
+          <t>-11,0; -4,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -2,97</t>
+          <t>-9,91; -3,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -4,01</t>
+          <t>-11,0; -4,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -2,97</t>
+          <t>-9,91; -3,13</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-50,67%</t>
+          <t>-50,98%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-50,67%</t>
+          <t>-50,98%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,61; -36,34</t>
+          <t>-76,32; -35,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -26,99</t>
+          <t>-67,39; -28,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,61; -36,34</t>
+          <t>-76,32; -35,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -26,99</t>
+          <t>-67,39; -28,21</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-1,97</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -5,97</t>
+          <t>-12,65; -6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; -0,71</t>
+          <t>-5,33; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -5,97</t>
+          <t>-12,65; -6,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; -0,71</t>
+          <t>-5,33; 1,44</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-19,35%</t>
+          <t>-8,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-19,35%</t>
+          <t>-8,48%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,99; -27,49</t>
+          <t>-50,39; -28,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,78; -3,76</t>
+          <t>-21,08; 7,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,99; -27,49</t>
+          <t>-50,39; -28,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,78; -3,76</t>
+          <t>-21,08; 7,24</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>3,76</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 0,36</t>
+          <t>-14,94; 0,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 11,93</t>
+          <t>-3,38; 11,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 0,36</t>
+          <t>-14,94; 0,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 11,93</t>
+          <t>-3,38; 11,45</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 0,42</t>
+          <t>-31,49; 1,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 31,0</t>
+          <t>-7,5; 30,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 0,42</t>
+          <t>-31,49; 1,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 31,0</t>
+          <t>-7,5; 30,06</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>1,54</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -4,34</t>
+          <t>-9,3; -4,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,73</t>
+          <t>-1,06; 4,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -4,34</t>
+          <t>-9,3; -4,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,73</t>
+          <t>-1,06; 4,2</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-0,48%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,48%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -19,98</t>
+          <t>-37,98; -19,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 12,4</t>
+          <t>-4,42; 19,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -19,98</t>
+          <t>-37,98; -19,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 12,4</t>
+          <t>-4,42; 19,19</t>
         </is>
       </c>
     </row>
